--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Evaluation Status</t>
+    <t>Cicada Evaluation Status</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The status of the result of an evaluation.</t>
+    <t>Extension codes for dose evaluation status beyond the HL7 THO immunization-evaluation-dose-status CodeSystem. Only codes not covered by the standard are defined here.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>1</t>
   </si>
   <si>
     <t>Level</t>
@@ -132,31 +132,13 @@
     <t>Definition</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>valid</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>not_valid</t>
-  </si>
-  <si>
-    <t>Not Valid</t>
-  </si>
-  <si>
     <t>extraneous</t>
   </si>
   <si>
     <t>Extraneous</t>
   </si>
   <si>
-    <t>sub_standard</t>
-  </si>
-  <si>
-    <t>Substandard</t>
+    <t>The dose was administered after the series was already complete. Every administered dose must be reported, so extraneous doses are tracked but do not affect the forecast.</t>
   </si>
 </sst>
 </file>
@@ -462,7 +444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -481,58 +463,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>41</v>
       </c>
       <c r="D2" t="s" s="2">
         <v>41</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +94,9 @@
   </si>
   <si>
     <t>Case Sensitive</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
   <si>
     <t>Value Set (all codes)</t>
@@ -331,110 +337,114 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -449,30 +459,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/cicada_ig/CodeSystem-EvalStatus.xlsx
+++ b/cicada_ig/CodeSystem-EvalStatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
